--- a/spreadsheets/domains/crampacs-med_CRAMPACS-MED_Workbook.xlsx
+++ b/spreadsheets/domains/crampacs-med_CRAMPACS-MED_Workbook.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="Re0fb9d692ede4beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R532a17d693944124"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R2e4921b91fa945c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R03aa2a575b2e4877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R148f7628b3e04fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="Rc8b49a697b4b4e45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="7" r:id="Rbea507156ef441f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R3faa9c42b0614c64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R12f989325f794db4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R72633a9ba16b4d1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R284d50247ad74020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R1450aae2e7e24757"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R4a1c208a4a374edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R4ea6cf2b90c74f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R9f9170f7f3024511"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -345,18 +346,24 @@
         <x:v>source_type</x:v>
       </x:c>
       <x:c r="E1" t="str">
+        <x:v>domain</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
         <x:v>source_role</x:v>
       </x:c>
-      <x:c r="F1" t="str">
+      <x:c r="G1" t="str">
+        <x:v>publication_or_snapshot_date</x:v>
+      </x:c>
+      <x:c r="H1" t="str">
         <x:v>unit_or_site</x:v>
       </x:c>
-      <x:c r="G1" t="str">
+      <x:c r="I1" t="str">
         <x:v>known_dependence</x:v>
       </x:c>
-      <x:c r="H1" t="str">
+      <x:c r="J1" t="str">
         <x:v>screening_status</x:v>
       </x:c>
-      <x:c r="I1" t="str">
+      <x:c r="K1" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
@@ -366,12 +373,16 @@
       <x:c r="C2" t="str"/>
       <x:c r="D2" t="str"/>
       <x:c r="E2" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F2" t="str">
         <x:v>positive_or_anomaly</x:v>
       </x:c>
-      <x:c r="F2" t="str"/>
       <x:c r="G2" t="str"/>
       <x:c r="H2" t="str"/>
       <x:c r="I2" t="str"/>
+      <x:c r="J2" t="str"/>
+      <x:c r="K2" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str"/>
@@ -379,12 +390,16 @@
       <x:c r="C3" t="str"/>
       <x:c r="D3" t="str"/>
       <x:c r="E3" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F3" t="str">
         <x:v>null_or_non_event</x:v>
       </x:c>
-      <x:c r="F3" t="str"/>
       <x:c r="G3" t="str"/>
       <x:c r="H3" t="str"/>
       <x:c r="I3" t="str"/>
+      <x:c r="J3" t="str"/>
+      <x:c r="K3" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -421,15 +436,18 @@
         <x:v>uncertainty_status</x:v>
       </x:c>
       <x:c r="I1" t="str">
+        <x:v>extraction_confidence</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
         <x:v>dependence_concern</x:v>
       </x:c>
-      <x:c r="J1" t="str">
+      <x:c r="K1" t="str">
         <x:v>bias_concern</x:v>
       </x:c>
-      <x:c r="K1" t="str">
+      <x:c r="L1" t="str">
         <x:v>null_or_non_event_flag</x:v>
       </x:c>
-      <x:c r="L1" t="str">
+      <x:c r="M1" t="str">
         <x:v>notes</x:v>
       </x:c>
     </x:row>
@@ -446,6 +464,7 @@
       <x:c r="J2" t="str"/>
       <x:c r="K2" t="str"/>
       <x:c r="L2" t="str"/>
+      <x:c r="M2" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -586,69 +605,91 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>Protocol</x:v>
+        <x:v>G0 Charter</x:v>
       </x:c>
       <x:c r="B3" t="str"/>
       <x:c r="C3" t="str"/>
       <x:c r="D3" t="str">
-        <x:v>Study charter, role assignment, protocol, candidate registry</x:v>
+        <x:v>decision statement, assurance level, roles, intended use, prohibited use</x:v>
       </x:c>
       <x:c r="E3" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>Extraction</x:v>
+        <x:v>G1 Coordinate Lock</x:v>
       </x:c>
       <x:c r="B4" t="str"/>
       <x:c r="C4" t="str"/>
       <x:c r="D4" t="str">
-        <x:v>Source flow, exclusions, row provenance, extraction confidence</x:v>
+        <x:v>coordinate ontology, candidate registry, tolerance basis, transform rules, negative controls</x:v>
       </x:c>
       <x:c r="E4" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>Normalization</x:v>
+        <x:v>G2 Source Universe</x:v>
       </x:c>
       <x:c r="B5" t="str"/>
       <x:c r="C5" t="str"/>
       <x:c r="D5" t="str">
-        <x:v>Raw values preserved, transforms registered, uncertainty assigned</x:v>
+        <x:v>search strategy, source catalog, source flow, exclusions, null search</x:v>
       </x:c>
       <x:c r="E5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>Independence and bias</x:v>
+        <x:v>G3 Row Integrity</x:v>
       </x:c>
       <x:c r="B6" t="str"/>
       <x:c r="C6" t="str"/>
       <x:c r="D6" t="str">
-        <x:v>Independence grades, bias review, missing evidence, weights</x:v>
+        <x:v>raw rows, source trace, extraction confidence, review status, quarantine log</x:v>
       </x:c>
       <x:c r="E6" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>Statistical</x:v>
+        <x:v>G4 Dependence and Bias</x:v>
       </x:c>
       <x:c r="B7" t="str"/>
       <x:c r="C7" t="str"/>
       <x:c r="D7" t="str">
-        <x:v>Primary statistic, null model, global correction, sensitivities</x:v>
+        <x:v>evidence-family map, independence grades, bias table, missing-evidence memo, weights</x:v>
       </x:c>
       <x:c r="E7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
-        <x:v>Release</x:v>
+        <x:v>G5 Statistical Method</x:v>
       </x:c>
       <x:c r="B8" t="str"/>
       <x:c r="C8" t="str"/>
       <x:c r="D8" t="str">
-        <x:v>Repro capsule, red team, signoff, claim language</x:v>
+        <x:v>primary statistic, null model, multiplicity correction, negative controls, sensitivity plan</x:v>
       </x:c>
       <x:c r="E8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>G6 Reproducibility</x:v>
+      </x:c>
+      <x:c r="B9" t="str"/>
+      <x:c r="C9" t="str"/>
+      <x:c r="D9" t="str">
+        <x:v>checksums, environment, run script, output hashes, clean-run report</x:v>
+      </x:c>
+      <x:c r="E9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>G7 Release</x:v>
+      </x:c>
+      <x:c r="B10" t="str"/>
+      <x:c r="C10" t="str"/>
+      <x:c r="D10" t="str">
+        <x:v>assurance case, red-team findings, decision memo, evidence tier, claim-language approval</x:v>
+      </x:c>
+      <x:c r="E10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -656,6 +697,153 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Binder</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Minimum records</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>00_charter</x:v>
+      </x:c>
+      <x:c r="B2" t="str"/>
+      <x:c r="C2" t="str"/>
+      <x:c r="D2" t="str">
+        <x:v>study_charter.md; role_assignment.csv</x:v>
+      </x:c>
+      <x:c r="E2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>01_protocol_lock</x:v>
+      </x:c>
+      <x:c r="B3" t="str"/>
+      <x:c r="C3" t="str"/>
+      <x:c r="D3" t="str">
+        <x:v>protocol.md; candidate_coordinate_registry.csv; amendment_log.csv</x:v>
+      </x:c>
+      <x:c r="E3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>02_sources</x:v>
+      </x:c>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+      <x:c r="D4" t="str">
+        <x:v>search_strategy.md; source_catalog.csv; source_flow.md</x:v>
+      </x:c>
+      <x:c r="E4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>03_extraction</x:v>
+      </x:c>
+      <x:c r="B5" t="str"/>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str">
+        <x:v>anomaly_rows_raw.csv; extraction_notes.md</x:v>
+      </x:c>
+      <x:c r="E5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>04_coordinate_normalization</x:v>
+      </x:c>
+      <x:c r="B6" t="str"/>
+      <x:c r="C6" t="str"/>
+      <x:c r="D6" t="str">
+        <x:v>coordinate_transform_registry.csv; normalized_rows.csv; unit_conversion_audit.md</x:v>
+      </x:c>
+      <x:c r="E6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>05_dependence_bias</x:v>
+      </x:c>
+      <x:c r="B7" t="str"/>
+      <x:c r="C7" t="str"/>
+      <x:c r="D7" t="str">
+        <x:v>independence_groups.csv; bias_assessment.csv; missing_evidence_assessment.md</x:v>
+      </x:c>
+      <x:c r="E7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>06_statistics</x:v>
+      </x:c>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str">
+        <x:v>statistical_analysis_plan.md; null_model_runs.csv; analysis_result.csv; negative_controls.md; sensitivity_results.md</x:v>
+      </x:c>
+      <x:c r="E8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>07_reproducibility</x:v>
+      </x:c>
+      <x:c r="B9" t="str"/>
+      <x:c r="C9" t="str"/>
+      <x:c r="D9" t="str">
+        <x:v>checksum_manifest.csv; environment_record.md; run_instructions.md; clean_run_report.md</x:v>
+      </x:c>
+      <x:c r="E9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>08_assurance_case</x:v>
+      </x:c>
+      <x:c r="B10" t="str"/>
+      <x:c r="C10" t="str"/>
+      <x:c r="D10" t="str">
+        <x:v>assurance_case.md; assurance_case_register.csv; risk_register.csv</x:v>
+      </x:c>
+      <x:c r="E10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>09_review_and_release</x:v>
+      </x:c>
+      <x:c r="B11" t="str"/>
+      <x:c r="C11" t="str"/>
+      <x:c r="D11" t="str">
+        <x:v>gate_review_record.csv; audit_report.md; decision_memo.md; claim_language_approval.md; release_signoff.md</x:v>
+      </x:c>
+      <x:c r="E11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>registers</x:v>
+      </x:c>
+      <x:c r="B12" t="str"/>
+      <x:c r="C12" t="str"/>
+      <x:c r="D12" t="str">
+        <x:v>document; control; gate; assurance; CAPA; decision; risk; training</x:v>
+      </x:c>
+      <x:c r="E12" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>

--- a/spreadsheets/domains/crampacs-med_CRAMPACS-MED_Workbook.xlsx
+++ b/spreadsheets/domains/crampacs-med_CRAMPACS-MED_Workbook.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R3faa9c42b0614c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R12f989325f794db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="R72633a9ba16b4d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R284d50247ad74020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R1450aae2e7e24757"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R4a1c208a4a374edb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="R4ea6cf2b90c74f4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R9f9170f7f3024511"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R75d2fcae364a402b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R4494524f1e4d4311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rea590633e9114261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Ra82f484c15994208"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="Ra8a077fd8cd54c05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R6abccc54590f4747"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rb14636e3d8844d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rc477c1b748484693"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/spreadsheets/domains/crampacs-med_CRAMPACS-MED_Workbook.xlsx
+++ b/spreadsheets/domains/crampacs-med_CRAMPACS-MED_Workbook.xlsx
@@ -2,14 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="R75d2fcae364a402b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R4494524f1e4d4311"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rea590633e9114261"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="Ra82f484c15994208"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="Ra8a077fd8cd54c05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R6abccc54590f4747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Rb14636e3d8844d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="Rc477c1b748484693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domain Summary" sheetId="1" r:id="Rfe6144aea898403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Scope" sheetId="2" r:id="R4e62578d91754f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Sources" sheetId="3" r:id="Rb62502c425f04775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preflight Rows" sheetId="4" r:id="R3ff0b2b2ade2474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gotchas" sheetId="5" r:id="R0aba76ad6ec54941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Gate" sheetId="6" r:id="R61ce72a9905f4651"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Full Evidence Binder" sheetId="7" r:id="Re38aef9f28b74f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Log" sheetId="8" r:id="R1071cdee0c88417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trust Checkpoints" sheetId="9" r:id="Rebc84d01911a4754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reliance Positioning" sheetId="10" r:id="R2c5d9e406d6c4aea"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -267,6 +269,61 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Field</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Entry</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>Trustworthy for</x:v>
+      </x:c>
+      <x:c r="B2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>Not trustworthy for</x:v>
+      </x:c>
+      <x:c r="B3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>Current assurance route</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>CRAMPACS-MED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>Current trust state</x:v>
+      </x:c>
+      <x:c r="B5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>Current evidence tier</x:v>
+      </x:c>
+      <x:c r="B6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>Prohibited claims</x:v>
+      </x:c>
+      <x:c r="B7" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -400,6 +457,276 @@
       <x:c r="I3" t="str"/>
       <x:c r="J3" t="str"/>
       <x:c r="K3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str"/>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+      <x:c r="D4" t="str"/>
+      <x:c r="E4" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F4" t="str"/>
+      <x:c r="G4" t="str"/>
+      <x:c r="H4" t="str"/>
+      <x:c r="I4" t="str"/>
+      <x:c r="J4" t="str"/>
+      <x:c r="K4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str"/>
+      <x:c r="B5" t="str"/>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str"/>
+      <x:c r="E5" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F5" t="str"/>
+      <x:c r="G5" t="str"/>
+      <x:c r="H5" t="str"/>
+      <x:c r="I5" t="str"/>
+      <x:c r="J5" t="str"/>
+      <x:c r="K5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str"/>
+      <x:c r="B6" t="str"/>
+      <x:c r="C6" t="str"/>
+      <x:c r="D6" t="str"/>
+      <x:c r="E6" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F6" t="str"/>
+      <x:c r="G6" t="str"/>
+      <x:c r="H6" t="str"/>
+      <x:c r="I6" t="str"/>
+      <x:c r="J6" t="str"/>
+      <x:c r="K6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str"/>
+      <x:c r="B7" t="str"/>
+      <x:c r="C7" t="str"/>
+      <x:c r="D7" t="str"/>
+      <x:c r="E7" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F7" t="str"/>
+      <x:c r="G7" t="str"/>
+      <x:c r="H7" t="str"/>
+      <x:c r="I7" t="str"/>
+      <x:c r="J7" t="str"/>
+      <x:c r="K7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str"/>
+      <x:c r="E8" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F8" t="str"/>
+      <x:c r="G8" t="str"/>
+      <x:c r="H8" t="str"/>
+      <x:c r="I8" t="str"/>
+      <x:c r="J8" t="str"/>
+      <x:c r="K8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str"/>
+      <x:c r="B9" t="str"/>
+      <x:c r="C9" t="str"/>
+      <x:c r="D9" t="str"/>
+      <x:c r="E9" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F9" t="str"/>
+      <x:c r="G9" t="str"/>
+      <x:c r="H9" t="str"/>
+      <x:c r="I9" t="str"/>
+      <x:c r="J9" t="str"/>
+      <x:c r="K9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str"/>
+      <x:c r="B10" t="str"/>
+      <x:c r="C10" t="str"/>
+      <x:c r="D10" t="str"/>
+      <x:c r="E10" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F10" t="str"/>
+      <x:c r="G10" t="str"/>
+      <x:c r="H10" t="str"/>
+      <x:c r="I10" t="str"/>
+      <x:c r="J10" t="str"/>
+      <x:c r="K10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str"/>
+      <x:c r="B11" t="str"/>
+      <x:c r="C11" t="str"/>
+      <x:c r="D11" t="str"/>
+      <x:c r="E11" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F11" t="str"/>
+      <x:c r="G11" t="str"/>
+      <x:c r="H11" t="str"/>
+      <x:c r="I11" t="str"/>
+      <x:c r="J11" t="str"/>
+      <x:c r="K11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str"/>
+      <x:c r="B12" t="str"/>
+      <x:c r="C12" t="str"/>
+      <x:c r="D12" t="str"/>
+      <x:c r="E12" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F12" t="str"/>
+      <x:c r="G12" t="str"/>
+      <x:c r="H12" t="str"/>
+      <x:c r="I12" t="str"/>
+      <x:c r="J12" t="str"/>
+      <x:c r="K12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str"/>
+      <x:c r="B13" t="str"/>
+      <x:c r="C13" t="str"/>
+      <x:c r="D13" t="str"/>
+      <x:c r="E13" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F13" t="str"/>
+      <x:c r="G13" t="str"/>
+      <x:c r="H13" t="str"/>
+      <x:c r="I13" t="str"/>
+      <x:c r="J13" t="str"/>
+      <x:c r="K13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str"/>
+      <x:c r="B14" t="str"/>
+      <x:c r="C14" t="str"/>
+      <x:c r="D14" t="str"/>
+      <x:c r="E14" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F14" t="str"/>
+      <x:c r="G14" t="str"/>
+      <x:c r="H14" t="str"/>
+      <x:c r="I14" t="str"/>
+      <x:c r="J14" t="str"/>
+      <x:c r="K14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str"/>
+      <x:c r="B15" t="str"/>
+      <x:c r="C15" t="str"/>
+      <x:c r="D15" t="str"/>
+      <x:c r="E15" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F15" t="str"/>
+      <x:c r="G15" t="str"/>
+      <x:c r="H15" t="str"/>
+      <x:c r="I15" t="str"/>
+      <x:c r="J15" t="str"/>
+      <x:c r="K15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str"/>
+      <x:c r="B16" t="str"/>
+      <x:c r="C16" t="str"/>
+      <x:c r="D16" t="str"/>
+      <x:c r="E16" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F16" t="str"/>
+      <x:c r="G16" t="str"/>
+      <x:c r="H16" t="str"/>
+      <x:c r="I16" t="str"/>
+      <x:c r="J16" t="str"/>
+      <x:c r="K16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str"/>
+      <x:c r="B17" t="str"/>
+      <x:c r="C17" t="str"/>
+      <x:c r="D17" t="str"/>
+      <x:c r="E17" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F17" t="str"/>
+      <x:c r="G17" t="str"/>
+      <x:c r="H17" t="str"/>
+      <x:c r="I17" t="str"/>
+      <x:c r="J17" t="str"/>
+      <x:c r="K17" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str"/>
+      <x:c r="B18" t="str"/>
+      <x:c r="C18" t="str"/>
+      <x:c r="D18" t="str"/>
+      <x:c r="E18" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F18" t="str"/>
+      <x:c r="G18" t="str"/>
+      <x:c r="H18" t="str"/>
+      <x:c r="I18" t="str"/>
+      <x:c r="J18" t="str"/>
+      <x:c r="K18" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str"/>
+      <x:c r="B19" t="str"/>
+      <x:c r="C19" t="str"/>
+      <x:c r="D19" t="str"/>
+      <x:c r="E19" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F19" t="str"/>
+      <x:c r="G19" t="str"/>
+      <x:c r="H19" t="str"/>
+      <x:c r="I19" t="str"/>
+      <x:c r="J19" t="str"/>
+      <x:c r="K19" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str"/>
+      <x:c r="B20" t="str"/>
+      <x:c r="C20" t="str"/>
+      <x:c r="D20" t="str"/>
+      <x:c r="E20" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F20" t="str"/>
+      <x:c r="G20" t="str"/>
+      <x:c r="H20" t="str"/>
+      <x:c r="I20" t="str"/>
+      <x:c r="J20" t="str"/>
+      <x:c r="K20" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str"/>
+      <x:c r="B21" t="str"/>
+      <x:c r="C21" t="str"/>
+      <x:c r="D21" t="str"/>
+      <x:c r="E21" t="str">
+        <x:v>med</x:v>
+      </x:c>
+      <x:c r="F21" t="str"/>
+      <x:c r="G21" t="str"/>
+      <x:c r="H21" t="str"/>
+      <x:c r="I21" t="str"/>
+      <x:c r="J21" t="str"/>
+      <x:c r="K21" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -466,6 +793,291 @@
       <x:c r="L2" t="str"/>
       <x:c r="M2" t="str"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str"/>
+      <x:c r="B3" t="str"/>
+      <x:c r="C3" t="str"/>
+      <x:c r="D3" t="str"/>
+      <x:c r="E3" t="str"/>
+      <x:c r="F3" t="str"/>
+      <x:c r="G3" t="str"/>
+      <x:c r="H3" t="str"/>
+      <x:c r="I3" t="str"/>
+      <x:c r="J3" t="str"/>
+      <x:c r="K3" t="str"/>
+      <x:c r="L3" t="str"/>
+      <x:c r="M3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str"/>
+      <x:c r="B4" t="str"/>
+      <x:c r="C4" t="str"/>
+      <x:c r="D4" t="str"/>
+      <x:c r="E4" t="str"/>
+      <x:c r="F4" t="str"/>
+      <x:c r="G4" t="str"/>
+      <x:c r="H4" t="str"/>
+      <x:c r="I4" t="str"/>
+      <x:c r="J4" t="str"/>
+      <x:c r="K4" t="str"/>
+      <x:c r="L4" t="str"/>
+      <x:c r="M4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str"/>
+      <x:c r="B5" t="str"/>
+      <x:c r="C5" t="str"/>
+      <x:c r="D5" t="str"/>
+      <x:c r="E5" t="str"/>
+      <x:c r="F5" t="str"/>
+      <x:c r="G5" t="str"/>
+      <x:c r="H5" t="str"/>
+      <x:c r="I5" t="str"/>
+      <x:c r="J5" t="str"/>
+      <x:c r="K5" t="str"/>
+      <x:c r="L5" t="str"/>
+      <x:c r="M5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str"/>
+      <x:c r="B6" t="str"/>
+      <x:c r="C6" t="str"/>
+      <x:c r="D6" t="str"/>
+      <x:c r="E6" t="str"/>
+      <x:c r="F6" t="str"/>
+      <x:c r="G6" t="str"/>
+      <x:c r="H6" t="str"/>
+      <x:c r="I6" t="str"/>
+      <x:c r="J6" t="str"/>
+      <x:c r="K6" t="str"/>
+      <x:c r="L6" t="str"/>
+      <x:c r="M6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str"/>
+      <x:c r="B7" t="str"/>
+      <x:c r="C7" t="str"/>
+      <x:c r="D7" t="str"/>
+      <x:c r="E7" t="str"/>
+      <x:c r="F7" t="str"/>
+      <x:c r="G7" t="str"/>
+      <x:c r="H7" t="str"/>
+      <x:c r="I7" t="str"/>
+      <x:c r="J7" t="str"/>
+      <x:c r="K7" t="str"/>
+      <x:c r="L7" t="str"/>
+      <x:c r="M7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str"/>
+      <x:c r="B8" t="str"/>
+      <x:c r="C8" t="str"/>
+      <x:c r="D8" t="str"/>
+      <x:c r="E8" t="str"/>
+      <x:c r="F8" t="str"/>
+      <x:c r="G8" t="str"/>
+      <x:c r="H8" t="str"/>
+      <x:c r="I8" t="str"/>
+      <x:c r="J8" t="str"/>
+      <x:c r="K8" t="str"/>
+      <x:c r="L8" t="str"/>
+      <x:c r="M8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str"/>
+      <x:c r="B9" t="str"/>
+      <x:c r="C9" t="str"/>
+      <x:c r="D9" t="str"/>
+      <x:c r="E9" t="str"/>
+      <x:c r="F9" t="str"/>
+      <x:c r="G9" t="str"/>
+      <x:c r="H9" t="str"/>
+      <x:c r="I9" t="str"/>
+      <x:c r="J9" t="str"/>
+      <x:c r="K9" t="str"/>
+      <x:c r="L9" t="str"/>
+      <x:c r="M9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str"/>
+      <x:c r="B10" t="str"/>
+      <x:c r="C10" t="str"/>
+      <x:c r="D10" t="str"/>
+      <x:c r="E10" t="str"/>
+      <x:c r="F10" t="str"/>
+      <x:c r="G10" t="str"/>
+      <x:c r="H10" t="str"/>
+      <x:c r="I10" t="str"/>
+      <x:c r="J10" t="str"/>
+      <x:c r="K10" t="str"/>
+      <x:c r="L10" t="str"/>
+      <x:c r="M10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str"/>
+      <x:c r="B11" t="str"/>
+      <x:c r="C11" t="str"/>
+      <x:c r="D11" t="str"/>
+      <x:c r="E11" t="str"/>
+      <x:c r="F11" t="str"/>
+      <x:c r="G11" t="str"/>
+      <x:c r="H11" t="str"/>
+      <x:c r="I11" t="str"/>
+      <x:c r="J11" t="str"/>
+      <x:c r="K11" t="str"/>
+      <x:c r="L11" t="str"/>
+      <x:c r="M11" t="str"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str"/>
+      <x:c r="B12" t="str"/>
+      <x:c r="C12" t="str"/>
+      <x:c r="D12" t="str"/>
+      <x:c r="E12" t="str"/>
+      <x:c r="F12" t="str"/>
+      <x:c r="G12" t="str"/>
+      <x:c r="H12" t="str"/>
+      <x:c r="I12" t="str"/>
+      <x:c r="J12" t="str"/>
+      <x:c r="K12" t="str"/>
+      <x:c r="L12" t="str"/>
+      <x:c r="M12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str"/>
+      <x:c r="B13" t="str"/>
+      <x:c r="C13" t="str"/>
+      <x:c r="D13" t="str"/>
+      <x:c r="E13" t="str"/>
+      <x:c r="F13" t="str"/>
+      <x:c r="G13" t="str"/>
+      <x:c r="H13" t="str"/>
+      <x:c r="I13" t="str"/>
+      <x:c r="J13" t="str"/>
+      <x:c r="K13" t="str"/>
+      <x:c r="L13" t="str"/>
+      <x:c r="M13" t="str"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str"/>
+      <x:c r="B14" t="str"/>
+      <x:c r="C14" t="str"/>
+      <x:c r="D14" t="str"/>
+      <x:c r="E14" t="str"/>
+      <x:c r="F14" t="str"/>
+      <x:c r="G14" t="str"/>
+      <x:c r="H14" t="str"/>
+      <x:c r="I14" t="str"/>
+      <x:c r="J14" t="str"/>
+      <x:c r="K14" t="str"/>
+      <x:c r="L14" t="str"/>
+      <x:c r="M14" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str"/>
+      <x:c r="B15" t="str"/>
+      <x:c r="C15" t="str"/>
+      <x:c r="D15" t="str"/>
+      <x:c r="E15" t="str"/>
+      <x:c r="F15" t="str"/>
+      <x:c r="G15" t="str"/>
+      <x:c r="H15" t="str"/>
+      <x:c r="I15" t="str"/>
+      <x:c r="J15" t="str"/>
+      <x:c r="K15" t="str"/>
+      <x:c r="L15" t="str"/>
+      <x:c r="M15" t="str"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str"/>
+      <x:c r="B16" t="str"/>
+      <x:c r="C16" t="str"/>
+      <x:c r="D16" t="str"/>
+      <x:c r="E16" t="str"/>
+      <x:c r="F16" t="str"/>
+      <x:c r="G16" t="str"/>
+      <x:c r="H16" t="str"/>
+      <x:c r="I16" t="str"/>
+      <x:c r="J16" t="str"/>
+      <x:c r="K16" t="str"/>
+      <x:c r="L16" t="str"/>
+      <x:c r="M16" t="str"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str"/>
+      <x:c r="B17" t="str"/>
+      <x:c r="C17" t="str"/>
+      <x:c r="D17" t="str"/>
+      <x:c r="E17" t="str"/>
+      <x:c r="F17" t="str"/>
+      <x:c r="G17" t="str"/>
+      <x:c r="H17" t="str"/>
+      <x:c r="I17" t="str"/>
+      <x:c r="J17" t="str"/>
+      <x:c r="K17" t="str"/>
+      <x:c r="L17" t="str"/>
+      <x:c r="M17" t="str"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str"/>
+      <x:c r="B18" t="str"/>
+      <x:c r="C18" t="str"/>
+      <x:c r="D18" t="str"/>
+      <x:c r="E18" t="str"/>
+      <x:c r="F18" t="str"/>
+      <x:c r="G18" t="str"/>
+      <x:c r="H18" t="str"/>
+      <x:c r="I18" t="str"/>
+      <x:c r="J18" t="str"/>
+      <x:c r="K18" t="str"/>
+      <x:c r="L18" t="str"/>
+      <x:c r="M18" t="str"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str"/>
+      <x:c r="B19" t="str"/>
+      <x:c r="C19" t="str"/>
+      <x:c r="D19" t="str"/>
+      <x:c r="E19" t="str"/>
+      <x:c r="F19" t="str"/>
+      <x:c r="G19" t="str"/>
+      <x:c r="H19" t="str"/>
+      <x:c r="I19" t="str"/>
+      <x:c r="J19" t="str"/>
+      <x:c r="K19" t="str"/>
+      <x:c r="L19" t="str"/>
+      <x:c r="M19" t="str"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str"/>
+      <x:c r="B20" t="str"/>
+      <x:c r="C20" t="str"/>
+      <x:c r="D20" t="str"/>
+      <x:c r="E20" t="str"/>
+      <x:c r="F20" t="str"/>
+      <x:c r="G20" t="str"/>
+      <x:c r="H20" t="str"/>
+      <x:c r="I20" t="str"/>
+      <x:c r="J20" t="str"/>
+      <x:c r="K20" t="str"/>
+      <x:c r="L20" t="str"/>
+      <x:c r="M20" t="str"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str"/>
+      <x:c r="B21" t="str"/>
+      <x:c r="C21" t="str"/>
+      <x:c r="D21" t="str"/>
+      <x:c r="E21" t="str"/>
+      <x:c r="F21" t="str"/>
+      <x:c r="G21" t="str"/>
+      <x:c r="H21" t="str"/>
+      <x:c r="I21" t="str"/>
+      <x:c r="J21" t="str"/>
+      <x:c r="K21" t="str"/>
+      <x:c r="L21" t="str"/>
+      <x:c r="M21" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -829,14 +1441,25 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="str">
-        <x:v>registers</x:v>
+        <x:v>10_trust_maintenance</x:v>
       </x:c>
       <x:c r="B12" t="str"/>
       <x:c r="C12" t="str"/>
       <x:c r="D12" t="str">
+        <x:v>build_ledger.csv; checkpoint_reviews.csv; assumption_uncertainty_log.csv; claim_trace_matrix.csv; trust_debt_register.csv; trust_status_summary.md; open_questions.md</x:v>
+      </x:c>
+      <x:c r="E12" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>registers</x:v>
+      </x:c>
+      <x:c r="B13" t="str"/>
+      <x:c r="C13" t="str"/>
+      <x:c r="D13" t="str">
         <x:v>document; control; gate; assurance; CAPA; decision; risk; training</x:v>
       </x:c>
-      <x:c r="E12" t="str"/>
+      <x:c r="E13" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -890,4 +1513,173 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" t="str">
+        <x:v>Checkpoint</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>Package point</x:v>
+      </x:c>
+      <x:c r="C1" t="str">
+        <x:v>Main honesty risk</x:v>
+      </x:c>
+      <x:c r="D1" t="str">
+        <x:v>Decision</x:v>
+      </x:c>
+      <x:c r="E1" t="str">
+        <x:v>Reviewer</x:v>
+      </x:c>
+      <x:c r="F1" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" t="str">
+        <x:v>T0</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>package start</x:v>
+      </x:c>
+      <x:c r="C2" t="str">
+        <x:v>unclear purpose or hidden intended use</x:v>
+      </x:c>
+      <x:c r="D2" t="str"/>
+      <x:c r="E2" t="str"/>
+      <x:c r="F2" t="str"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" t="str">
+        <x:v>T1</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>coordinate proposed</x:v>
+      </x:c>
+      <x:c r="C3" t="str">
+        <x:v>coordinate drift or tolerance creep</x:v>
+      </x:c>
+      <x:c r="D3" t="str"/>
+      <x:c r="E3" t="str"/>
+      <x:c r="F3" t="str"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" t="str">
+        <x:v>T2</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>sources drafted</x:v>
+      </x:c>
+      <x:c r="C4" t="str">
+        <x:v>positive-only evidence</x:v>
+      </x:c>
+      <x:c r="D4" t="str"/>
+      <x:c r="E4" t="str"/>
+      <x:c r="F4" t="str"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>T3</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>rows extracted</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>source trace or AI-summary drift</x:v>
+      </x:c>
+      <x:c r="D5" t="str"/>
+      <x:c r="E5" t="str"/>
+      <x:c r="F5" t="str"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>T4</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>normalization drafted</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>hidden unit conversion</x:v>
+      </x:c>
+      <x:c r="D6" t="str"/>
+      <x:c r="E6" t="str"/>
+      <x:c r="F6" t="str"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>T5</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>dependence and bias drafted</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>duplicate evidence counted independently</x:v>
+      </x:c>
+      <x:c r="D7" t="str"/>
+      <x:c r="E7" t="str"/>
+      <x:c r="F7" t="str"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>T6</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>statistics planned</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>statistic shopping or weak null</x:v>
+      </x:c>
+      <x:c r="D8" t="str"/>
+      <x:c r="E8" t="str"/>
+      <x:c r="F8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>T7</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>results generated</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>local result overclaimed</x:v>
+      </x:c>
+      <x:c r="D9" t="str"/>
+      <x:c r="E9" t="str"/>
+      <x:c r="F9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>T8</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>report drafted</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>claim exceeds evidence tier</x:v>
+      </x:c>
+      <x:c r="D10" t="str"/>
+      <x:c r="E10" t="str"/>
+      <x:c r="F10" t="str"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>T9</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>release review</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>unknown trust state</x:v>
+      </x:c>
+      <x:c r="D11" t="str"/>
+      <x:c r="E11" t="str"/>
+      <x:c r="F11" t="str"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>